--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Deception_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Deception_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rb0d3d6e5ec2c4092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R9d784743bc1844a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R0be90f9f076c4b6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R2e52b2181cc04dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R547bf4c585f54c0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R597a4a9b2d4b48a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R47d9fb9dc6684895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R11cca12b70d84d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R8d30432d3b304634"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R5157079adf914e81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Re7fddfe27dae43c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R4a9736b23a11404e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R8a85ea7bda2b4de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R3a112d7f61424828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R0d2eb6b0ead94401"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R8a49b631064b4749"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R518824b5973e4ce4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R019848f910954994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R515fbfa21d6c46bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R0dc6e915a01b4631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rce44c03955c543cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rec5d7dca4a30420b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re5e1e052943c4efc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R2e7f0fc440f94326"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R60e7a999a1af4f12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R1ad24c239d8e421b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rfd341d96a0274263"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2f05f536057840cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcbfd759c7168486e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R767331d4c4814e45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R0322f1b5251646b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R0c133594f4e24867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R3c1c7568e1ef4624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R2b6f1b60505742e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R6757b90cdf0c4857"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R22c27139b38b4404"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7c4f6ec7a5514806"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1876778f1374438d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R51bc823b2e624d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R07213d2937094275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R42e25a376cfb44cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R0ca351dfd8d940ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3908b85289e9454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R099d5efa5f664aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R377aa137b33d4359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdb0f56863d384889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R582aac9dfc9b4a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcff23ae6e72141d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rf2a0e14617b44c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rf72dc2f6a6414494"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R5407c882b30c4348"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rff52a506fe5044de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb691a1a88bae448a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re28b0faf184743e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R2f39a98e721448d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb99bd41aa8914349"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="44">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2099,7 +2093,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="34" t="n">
+      <x:c r="B5" s="32" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>160</x:v>
       </x:c>
@@ -2107,7 +2101,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="34" t="n">
+      <x:c r="E5" s="32" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2115,7 +2109,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="34" t="n">
+      <x:c r="H5" s="32" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>18</x:v>
       </x:c>
@@ -2123,7 +2117,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="34" t="n">
+      <x:c r="K5" s="32" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>132</x:v>
       </x:c>
@@ -2146,7 +2140,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="35" t="str">
+      <x:c r="A7" s="33" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2178,95 +2172,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="36" t="str">
+      <x:c r="A10" s="34" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="40" t="n">
+      <x:c r="B10" s="38" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C10" s="40" t="n">
+      <x:c r="C10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="40" t="n">
+      <x:c r="D10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="40" t="n">
+      <x:c r="E10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="40" t="n">
+      <x:c r="F10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="40" t="n">
+      <x:c r="G10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H10" s="40" t="n">
+      <x:c r="H10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I10" s="40" t="n">
+      <x:c r="I10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="40" t="n">
+      <x:c r="J10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="40" t="n">
+      <x:c r="K10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="40" t="n">
+      <x:c r="L10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="40" t="n">
+      <x:c r="M10" s="38" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2275,104 +2269,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="41" t="n">
+      <x:c r="B11" s="39" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="41" t="n">
+      <x:c r="C11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D11" s="41" t="n">
+      <x:c r="D11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="41" t="n">
+      <x:c r="E11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="41" t="n">
+      <x:c r="F11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="41" t="n">
+      <x:c r="G11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H11" s="41" t="n">
+      <x:c r="H11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I11" s="41" t="n">
+      <x:c r="I11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="41" t="n">
+      <x:c r="J11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="41" t="n">
+      <x:c r="K11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="41" t="n">
+      <x:c r="L11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="41" t="n">
+      <x:c r="M11" s="39" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="36" t="str">
+      <x:c r="A12" s="34" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="40" t="n">
+      <x:c r="B12" s="38" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C12" s="40" t="n">
+      <x:c r="C12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="38" t="n">
+        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D12" s="40" t="n">
-        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="40" t="n">
+      <x:c r="E12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="40" t="n">
+      <x:c r="F12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="40" t="n">
+      <x:c r="G12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H12" s="40" t="n">
+      <x:c r="H12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="40" t="n">
+      <x:c r="I12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="40" t="n">
+      <x:c r="J12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="40" t="n">
+      <x:c r="K12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="40" t="n">
+      <x:c r="L12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="40" t="n">
+      <x:c r="M12" s="38" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2381,104 +2375,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="41" t="n">
+      <x:c r="B13" s="39" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="41" t="n">
+      <x:c r="C13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D13" s="41" t="n">
+      <x:c r="D13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="41" t="n">
+      <x:c r="E13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="41" t="n">
+      <x:c r="F13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="41" t="n">
+      <x:c r="G13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H13" s="41" t="n">
+      <x:c r="H13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I13" s="41" t="n">
+      <x:c r="I13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="41" t="n">
+      <x:c r="J13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="41" t="n">
+      <x:c r="K13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="41" t="n">
+      <x:c r="L13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="41" t="n">
+      <x:c r="M13" s="39" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="36" t="str">
+      <x:c r="A14" s="34" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="40" t="n">
+      <x:c r="B14" s="38" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="40" t="n">
+      <x:c r="C14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="40" t="n">
+      <x:c r="D14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="40" t="n">
+      <x:c r="E14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="40" t="n">
+      <x:c r="F14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="40" t="n">
+      <x:c r="G14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="40" t="n">
+      <x:c r="H14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="40" t="n">
+      <x:c r="I14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="40" t="n">
+      <x:c r="J14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="40" t="n">
+      <x:c r="K14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="40" t="n">
+      <x:c r="L14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="40" t="n">
+      <x:c r="M14" s="38" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2487,104 +2481,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="41" t="n">
+      <x:c r="B15" s="39" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="41" t="n">
+      <x:c r="C15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="41" t="n">
+      <x:c r="D15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="41" t="n">
+      <x:c r="E15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="41" t="n">
+      <x:c r="F15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="41" t="n">
+      <x:c r="G15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="41" t="n">
+      <x:c r="H15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="41" t="n">
+      <x:c r="I15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="41" t="n">
+      <x:c r="J15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="41" t="n">
+      <x:c r="K15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="41" t="n">
+      <x:c r="L15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="41" t="n">
+      <x:c r="M15" s="39" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="36" t="str">
+      <x:c r="A16" s="34" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="40" t="n">
+      <x:c r="B16" s="38" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="40" t="n">
+      <x:c r="C16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="40" t="n">
+      <x:c r="D16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="40" t="n">
+      <x:c r="E16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="40" t="n">
+      <x:c r="F16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="40" t="n">
+      <x:c r="G16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="40" t="n">
+      <x:c r="H16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="40" t="n">
+      <x:c r="I16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="40" t="n">
+      <x:c r="J16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="40" t="n">
+      <x:c r="K16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="40" t="n">
+      <x:c r="L16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="40" t="n">
+      <x:c r="M16" s="38" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2593,104 +2587,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="41" t="n">
+      <x:c r="B17" s="39" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="41" t="n">
+      <x:c r="C17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="41" t="n">
+      <x:c r="D17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="41" t="n">
+      <x:c r="E17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="41" t="n">
+      <x:c r="F17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="41" t="n">
+      <x:c r="G17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="41" t="n">
+      <x:c r="H17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I17" s="41" t="n">
+      <x:c r="I17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="41" t="n">
+      <x:c r="J17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="41" t="n">
+      <x:c r="K17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="41" t="n">
+      <x:c r="L17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="41" t="n">
+      <x:c r="M17" s="39" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="36" t="str">
+      <x:c r="A18" s="34" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="40" t="n">
+      <x:c r="B18" s="38" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="40" t="n">
+      <x:c r="C18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="40" t="n">
+      <x:c r="D18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="40" t="n">
+      <x:c r="E18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="40" t="n">
+      <x:c r="F18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="40" t="n">
+      <x:c r="G18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="40" t="n">
+      <x:c r="H18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="40" t="n">
+      <x:c r="I18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="40" t="n">
+      <x:c r="J18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="40" t="n">
+      <x:c r="K18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="40" t="n">
+      <x:c r="L18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="40" t="n">
+      <x:c r="M18" s="38" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2699,104 +2693,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="41" t="n">
+      <x:c r="B19" s="39" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="41" t="n">
+      <x:c r="C19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="41" t="n">
+      <x:c r="D19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="41" t="n">
+      <x:c r="E19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="41" t="n">
+      <x:c r="F19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="41" t="n">
+      <x:c r="G19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="41" t="n">
+      <x:c r="H19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="41" t="n">
+      <x:c r="I19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="41" t="n">
+      <x:c r="J19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="41" t="n">
+      <x:c r="K19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="41" t="n">
+      <x:c r="L19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="41" t="n">
+      <x:c r="M19" s="39" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="36" t="str">
+      <x:c r="A20" s="34" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="40" t="n">
+      <x:c r="B20" s="38" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="40" t="n">
+      <x:c r="C20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="40" t="n">
+      <x:c r="D20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="40" t="n">
+      <x:c r="E20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="40" t="n">
+      <x:c r="F20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="40" t="n">
+      <x:c r="G20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="40" t="n">
+      <x:c r="H20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="40" t="n">
+      <x:c r="I20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="40" t="n">
+      <x:c r="J20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="40" t="n">
+      <x:c r="K20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="40" t="n">
+      <x:c r="L20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="40" t="n">
+      <x:c r="M20" s="38" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2805,104 +2799,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="41" t="n">
+      <x:c r="B21" s="39" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="41" t="n">
+      <x:c r="C21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="41" t="n">
+      <x:c r="D21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="41" t="n">
+      <x:c r="E21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="41" t="n">
+      <x:c r="F21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="41" t="n">
+      <x:c r="G21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="41" t="n">
+      <x:c r="H21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="41" t="n">
+      <x:c r="I21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="41" t="n">
+      <x:c r="J21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="41" t="n">
+      <x:c r="K21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="41" t="n">
+      <x:c r="L21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="41" t="n">
+      <x:c r="M21" s="39" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="36" t="str">
+      <x:c r="A22" s="34" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="40" t="n">
+      <x:c r="B22" s="38" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="40" t="n">
+      <x:c r="C22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="40" t="n">
+      <x:c r="D22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="40" t="n">
+      <x:c r="E22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="40" t="n">
+      <x:c r="F22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="40" t="n">
+      <x:c r="G22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="40" t="n">
+      <x:c r="H22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="40" t="n">
+      <x:c r="I22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="40" t="n">
+      <x:c r="J22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="40" t="n">
+      <x:c r="K22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="40" t="n">
+      <x:c r="L22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="40" t="n">
+      <x:c r="M22" s="38" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2911,104 +2905,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="41" t="n">
+      <x:c r="B23" s="39" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="41" t="n">
+      <x:c r="C23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="41" t="n">
+      <x:c r="D23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="41" t="n">
+      <x:c r="E23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="41" t="n">
+      <x:c r="F23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="41" t="n">
+      <x:c r="G23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="41" t="n">
+      <x:c r="H23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="41" t="n">
+      <x:c r="I23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="41" t="n">
+      <x:c r="J23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="41" t="n">
+      <x:c r="K23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="41" t="n">
+      <x:c r="L23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="41" t="n">
+      <x:c r="M23" s="39" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="36" t="str">
+      <x:c r="A24" s="34" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="40" t="n">
+      <x:c r="B24" s="38" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C24" s="40" t="n">
+      <x:c r="C24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D24" s="40" t="n">
+      <x:c r="D24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="40" t="n">
+      <x:c r="E24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="40" t="n">
+      <x:c r="F24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="40" t="n">
+      <x:c r="G24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="40" t="n">
+      <x:c r="H24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="40" t="n">
+      <x:c r="I24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="40" t="n">
+      <x:c r="J24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="40" t="n">
+      <x:c r="K24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="40" t="n">
+      <x:c r="L24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="40" t="n">
+      <x:c r="M24" s="38" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3017,104 +3011,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="41" t="n">
+      <x:c r="B25" s="39" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C25" s="41" t="n">
+      <x:c r="C25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" s="41" t="n">
+      <x:c r="D25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="41" t="n">
+      <x:c r="E25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="41" t="n">
+      <x:c r="F25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="41" t="n">
+      <x:c r="G25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="41" t="n">
+      <x:c r="H25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I25" s="41" t="n">
+      <x:c r="I25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="41" t="n">
+      <x:c r="J25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="41" t="n">
+      <x:c r="K25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="41" t="n">
+      <x:c r="L25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="41" t="n">
+      <x:c r="M25" s="39" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="36" t="str">
+      <x:c r="A26" s="34" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="40" t="n">
+      <x:c r="B26" s="38" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C26" s="40" t="n">
+      <x:c r="C26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D26" s="40" t="n">
+      <x:c r="D26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="40" t="n">
+      <x:c r="E26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="40" t="n">
+      <x:c r="F26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="40" t="n">
+      <x:c r="G26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="40" t="n">
+      <x:c r="H26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I26" s="40" t="n">
+      <x:c r="I26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="40" t="n">
+      <x:c r="J26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="40" t="n">
+      <x:c r="K26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="40" t="n">
+      <x:c r="L26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="40" t="n">
+      <x:c r="M26" s="38" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3123,104 +3117,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="41" t="n">
+      <x:c r="B27" s="39" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="41" t="n">
+      <x:c r="C27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="41" t="n">
+      <x:c r="D27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="41" t="n">
+      <x:c r="E27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="41" t="n">
+      <x:c r="F27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="41" t="n">
+      <x:c r="G27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="41" t="n">
+      <x:c r="H27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="41" t="n">
+      <x:c r="I27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="41" t="n">
+      <x:c r="J27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="41" t="n">
+      <x:c r="K27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="41" t="n">
+      <x:c r="L27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="41" t="n">
+      <x:c r="M27" s="39" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="36" t="str">
+      <x:c r="A28" s="34" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="40" t="n">
+      <x:c r="B28" s="38" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="40" t="n">
+      <x:c r="C28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="40" t="n">
+      <x:c r="D28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="40" t="n">
+      <x:c r="E28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="40" t="n">
+      <x:c r="F28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="40" t="n">
+      <x:c r="G28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="40" t="n">
+      <x:c r="H28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="40" t="n">
+      <x:c r="I28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="40" t="n">
+      <x:c r="J28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="40" t="n">
+      <x:c r="K28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="40" t="n">
+      <x:c r="L28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="40" t="n">
+      <x:c r="M28" s="38" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3229,104 +3223,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="41" t="n">
+      <x:c r="B29" s="39" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="41" t="n">
+      <x:c r="C29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="41" t="n">
+      <x:c r="D29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="41" t="n">
+      <x:c r="E29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="41" t="n">
+      <x:c r="F29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="41" t="n">
+      <x:c r="G29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="41" t="n">
+      <x:c r="H29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="41" t="n">
+      <x:c r="I29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="41" t="n">
+      <x:c r="J29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="41" t="n">
+      <x:c r="K29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="41" t="n">
+      <x:c r="L29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="41" t="n">
+      <x:c r="M29" s="39" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="36" t="str">
+      <x:c r="A30" s="34" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="40" t="n">
+      <x:c r="B30" s="38" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="40" t="n">
+      <x:c r="C30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="40" t="n">
+      <x:c r="D30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="40" t="n">
+      <x:c r="E30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="40" t="n">
+      <x:c r="F30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="40" t="n">
+      <x:c r="G30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="40" t="n">
+      <x:c r="H30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="40" t="n">
+      <x:c r="I30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="40" t="n">
+      <x:c r="J30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="40" t="n">
+      <x:c r="K30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="40" t="n">
+      <x:c r="L30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="40" t="n">
+      <x:c r="M30" s="38" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3335,104 +3329,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="41" t="n">
+      <x:c r="B31" s="39" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="41" t="n">
+      <x:c r="C31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="41" t="n">
+      <x:c r="D31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="41" t="n">
+      <x:c r="E31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="41" t="n">
+      <x:c r="F31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="41" t="n">
+      <x:c r="G31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="41" t="n">
+      <x:c r="H31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="41" t="n">
+      <x:c r="I31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="41" t="n">
+      <x:c r="J31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="41" t="n">
+      <x:c r="K31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="41" t="n">
+      <x:c r="L31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="41" t="n">
+      <x:c r="M31" s="39" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="36" t="str">
+      <x:c r="A32" s="34" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="40" t="n">
+      <x:c r="B32" s="38" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="40" t="n">
+      <x:c r="C32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="40" t="n">
+      <x:c r="D32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="40" t="n">
+      <x:c r="E32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="40" t="n">
+      <x:c r="F32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="40" t="n">
+      <x:c r="G32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="40" t="n">
+      <x:c r="H32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="40" t="n">
+      <x:c r="I32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="40" t="n">
+      <x:c r="J32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="40" t="n">
+      <x:c r="K32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="40" t="n">
+      <x:c r="L32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="40" t="n">
+      <x:c r="M32" s="38" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3441,104 +3435,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="41" t="n">
+      <x:c r="B33" s="39" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="41" t="n">
+      <x:c r="C33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="41" t="n">
+      <x:c r="D33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="41" t="n">
+      <x:c r="E33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="41" t="n">
+      <x:c r="F33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="41" t="n">
+      <x:c r="G33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="41" t="n">
+      <x:c r="H33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="41" t="n">
+      <x:c r="I33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="41" t="n">
+      <x:c r="J33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="41" t="n">
+      <x:c r="K33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="41" t="n">
+      <x:c r="L33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="41" t="n">
+      <x:c r="M33" s="39" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="36" t="str">
+      <x:c r="A34" s="34" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="40" t="n">
+      <x:c r="B34" s="38" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="40" t="n">
+      <x:c r="C34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="40" t="n">
+      <x:c r="D34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="40" t="n">
+      <x:c r="E34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="40" t="n">
+      <x:c r="F34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="40" t="n">
+      <x:c r="G34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="40" t="n">
+      <x:c r="H34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="40" t="n">
+      <x:c r="I34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="40" t="n">
+      <x:c r="J34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="40" t="n">
+      <x:c r="K34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="40" t="n">
+      <x:c r="L34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="40" t="n">
+      <x:c r="M34" s="38" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3547,119 +3541,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="41" t="n">
+      <x:c r="B35" s="39" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$17)</x:f>
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C35" s="41" t="n">
+      <x:c r="C35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$17,"Défini")</x:f>
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D35" s="41" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$17,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E35" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$17,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="41" t="n">
+      <x:c r="F35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$17,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="41" t="n">
+      <x:c r="G35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$17,"Établi")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H35" s="41" t="n">
+      <x:c r="H35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$17,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="41" t="n">
+      <x:c r="I35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$17,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J35" s="41" t="n">
+      <x:c r="J35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$17,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="41" t="n">
+      <x:c r="K35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$17,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="41" t="n">
+      <x:c r="L35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$17,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="41" t="n">
+      <x:c r="M35" s="39" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$17,"P0")</x:f>
         <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="41"/>
-      <x:c r="C36" s="41"/>
-      <x:c r="D36" s="41"/>
-      <x:c r="E36" s="41"/>
-      <x:c r="F36" s="41"/>
-      <x:c r="G36" s="41"/>
-      <x:c r="H36" s="41"/>
-      <x:c r="I36" s="41"/>
-      <x:c r="J36" s="41"/>
-      <x:c r="K36" s="41"/>
-      <x:c r="L36" s="41"/>
-      <x:c r="M36" s="41"/>
+      <x:c r="B36" s="39"/>
+      <x:c r="C36" s="39"/>
+      <x:c r="D36" s="39"/>
+      <x:c r="E36" s="39"/>
+      <x:c r="F36" s="39"/>
+      <x:c r="G36" s="39"/>
+      <x:c r="H36" s="39"/>
+      <x:c r="I36" s="39"/>
+      <x:c r="J36" s="39"/>
+      <x:c r="K36" s="39"/>
+      <x:c r="L36" s="39"/>
+      <x:c r="M36" s="39"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="42" t="n">
+      <x:c r="B37" s="40" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>160</x:v>
       </x:c>
-      <x:c r="C37" s="42" t="n">
+      <x:c r="C37" s="40" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D37" s="42" t="n">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D37" s="40" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="42" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E37" s="40" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="42" t="n">
+      <x:c r="F37" s="40" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="42" t="n">
+      <x:c r="G37" s="40" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H37" s="42" t="n">
+      <x:c r="H37" s="40" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>18</x:v>
       </x:c>
-      <x:c r="I37" s="42" t="n">
+      <x:c r="I37" s="40" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>132</x:v>
       </x:c>
-      <x:c r="J37" s="42" t="n">
+      <x:c r="J37" s="40" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="42" t="n">
+      <x:c r="K37" s="40" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="42" t="n">
+      <x:c r="L37" s="40" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="42" t="n">
+      <x:c r="M37" s="40" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>24</x:v>
       </x:c>
@@ -3883,61 +3877,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -3987,8 +3981,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4038,8 +4032,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4089,8 +4083,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4140,8 +4134,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4177,7 +4171,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R898f0f779ccc4a7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f6561af3174015"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4317,61 +4311,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4423,8 +4417,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4474,8 +4468,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4525,8 +4519,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4576,8 +4570,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4627,8 +4621,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4678,8 +4672,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4729,8 +4723,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4780,8 +4774,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4815,7 +4809,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57b70b3acaab4caf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7a35d767ce340d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4955,61 +4949,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5061,8 +5055,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5112,8 +5106,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5163,8 +5157,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5214,8 +5208,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5265,8 +5259,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5316,8 +5310,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5367,8 +5361,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5418,8 +5412,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5453,7 +5447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e6e343d39474332"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33a50d6c48f3461e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5593,61 +5587,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5699,8 +5693,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5750,8 +5744,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5801,8 +5795,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5852,8 +5846,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5903,8 +5897,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5954,8 +5948,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6005,8 +5999,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6056,8 +6050,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6091,7 +6085,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd126bc441b2c4338"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bd34340d7194603"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6231,61 +6225,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6337,8 +6331,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6390,8 +6384,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6443,8 +6437,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6496,8 +6490,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6549,8 +6543,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6602,8 +6596,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6655,8 +6649,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6708,8 +6702,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6761,8 +6755,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6814,8 +6808,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6851,7 +6845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d3e1b64cfd4225"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ba30fb30204827"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6991,61 +6985,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7097,8 +7091,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7148,8 +7142,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7199,8 +7193,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7250,8 +7244,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7301,8 +7295,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7352,8 +7346,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7403,8 +7397,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7454,8 +7448,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7489,7 +7483,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R634af1178527470b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e193e0a2ab54025"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7629,74 +7623,74 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="2"/>
-      <x:c r="B7" s="33" t="str">
+      <x:c r="B7" s="31" t="str">
         <x:v>Aucun élément inventorié. Voir les limites dans Guide.</x:v>
       </x:c>
-      <x:c r="C7" s="33"/>
-      <x:c r="D7" s="33"/>
-      <x:c r="E7" s="33"/>
-      <x:c r="F7" s="33"/>
-      <x:c r="G7" s="33"/>
+      <x:c r="C7" s="31"/>
+      <x:c r="D7" s="31"/>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="31"/>
+      <x:c r="G7" s="31"/>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="2"/>
@@ -7850,61 +7844,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7950,10 +7944,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7999,10 +7993,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8048,10 +8042,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DEC-SRC-SUITS</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.videogamer.com/bioware-unhappy-with-mass-effect-novel-continuity-errors/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8087,7 +8081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce320e8822f5463f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69392d9a37194bcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8227,61 +8221,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8327,10 +8321,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200763/mass-effect-deception-by-william-c-dietz/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8376,10 +8370,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8415,7 +8409,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23cb60193d9e44db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc43314f3dbb94f66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8555,61 +8549,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8659,8 +8653,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8708,8 +8702,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8757,8 +8751,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8806,8 +8800,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8855,8 +8849,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8904,8 +8898,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -8939,7 +8933,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf142e03db36466c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55e8734a7387464b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9079,61 +9073,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9179,10 +9173,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200763/mass-effect-deception-by-william-c-dietz/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9228,10 +9222,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9277,10 +9271,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DEC-SRC-AND</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9326,10 +9320,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DEC-SRC-AND</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9365,7 +9359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R972e9255a0064c14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04387a4fb548435d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9505,61 +9499,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9611,8 +9605,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9662,8 +9656,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9713,8 +9707,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9764,8 +9758,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9799,7 +9793,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde8771634cc84136"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9717aa9cd44f0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9939,61 +9933,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10045,8 +10039,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10096,8 +10090,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10147,8 +10141,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10198,8 +10192,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10249,8 +10243,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10300,8 +10294,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10351,8 +10345,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10402,8 +10396,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10453,8 +10447,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10504,8 +10498,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10539,7 +10533,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7289b2ea5c9e4b11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42e15ec931974030"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10679,61 +10673,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10785,8 +10779,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10836,8 +10830,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10887,8 +10881,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10938,8 +10932,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10989,8 +10983,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11040,8 +11034,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11091,8 +11085,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11142,8 +11136,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11193,8 +11187,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11244,8 +11238,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11279,7 +11273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2361e9a5f1b4d0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0d7ca4ac98b4e34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11419,61 +11413,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11525,8 +11519,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11576,8 +11570,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11627,8 +11621,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11678,8 +11672,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11713,7 +11707,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477035bb42624a88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae03af3f4c484739"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11853,61 +11847,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11957,8 +11951,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12006,8 +12000,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12055,8 +12049,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12104,8 +12098,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12153,8 +12147,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12188,7 +12182,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcecab2aee7374d65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57cbe1bf08764b09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12328,61 +12322,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12432,8 +12426,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12481,8 +12475,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12530,8 +12524,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12579,8 +12573,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12628,8 +12622,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12677,8 +12671,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12726,8 +12720,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12775,8 +12769,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12810,7 +12804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2301e7a0a04b4f78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8660fb88b7c34c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12950,61 +12944,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13056,8 +13050,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13107,8 +13101,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13158,8 +13152,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13209,8 +13203,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13260,8 +13254,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13311,8 +13305,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13362,8 +13356,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13413,8 +13407,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13456,8 +13450,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13499,8 +13493,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13542,8 +13536,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13585,8 +13579,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13620,7 +13614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f6e9da6081a415b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra75b034bf72b46b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13647,7 +13641,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="91" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -13760,61 +13754,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13826,7 +13820,7 @@
         <x:v>Annonce de révision</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -13845,7 +13839,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>continuity/dec.json ; règle documentée et décision de validation datée.</x:v>
+        <x:v>Référence documentaire DEC-CON-01 consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -13860,11 +13854,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-PRESS</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.gamespot.com/articles/bioware-apologizes-for-mass-effect-novel-errors/1100-6349818/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -13875,7 +13869,7 @@
         <x:v>Gillian : âge incohérent</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -13894,7 +13888,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>continuity/dec.json ; règle documentée et décision de validation datée.</x:v>
+        <x:v>Référence documentaire DEC-CON-02 consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -13909,11 +13903,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-GIL</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Gillian_Grayson</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
@@ -13924,7 +13918,7 @@
         <x:v>Nick : âge incohérent</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -13943,7 +13937,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>continuity/dec.json ; règle documentée et décision de validation datée.</x:v>
+        <x:v>Référence documentaire DEC-CON-03 consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -13958,11 +13952,11 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DEC-SRC-NICK</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nick_Donahue</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
+      <x:c r="S9" s="9" t="str">
+        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
@@ -14007,10 +14001,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DEC-SRC-SUITS</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://www.videogamer.com/bioware-unhappy-with-mass-effect-novel-continuity-errors/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14056,10 +14050,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>DEC-SRC-CRITIQUE</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/User_blog%3AElseweyr/Errors_in_Deception_%22Errors%22</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14103,8 +14097,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14116,7 +14110,7 @@
         <x:v>Édition corrigée non attestée</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
         <x:v>Établi</x:v>
@@ -14135,7 +14129,7 @@
       <x:c r="J13" s="9" t="str"/>
       <x:c r="K13" s="9" t="str"/>
       <x:c r="L13" s="9" t="str">
-        <x:v>continuity/dec.json ; règle documentée et décision de validation datée.</x:v>
+        <x:v>Référence documentaire DEC-CON-07 consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -14150,11 +14144,11 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>DEC-SRC-WIKI</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect:_Deception</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
-        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
+      <x:c r="S13" s="9" t="str">
+        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="82" customHeight="1">
@@ -14199,10 +14193,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>DEC-SRC-TIMELINE</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Timeline</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14246,8 +14240,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14291,8 +14285,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14304,7 +14298,7 @@
         <x:v>Bibliographie</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D17" s="16" t="str">
         <x:v>Établi</x:v>
@@ -14323,7 +14317,7 @@
       <x:c r="J17" s="9" t="str"/>
       <x:c r="K17" s="9" t="str"/>
       <x:c r="L17" s="9" t="str">
-        <x:v>continuity/dec.json ; règle documentée et décision de validation datée.</x:v>
+        <x:v>Référence documentaire DEC-CON-11 consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M17" s="9" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -14338,11 +14332,11 @@
       <x:c r="Q17" s="9" t="str">
         <x:v>DEC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R17" s="20" t="str">
+      <x:c r="R17" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200763/mass-effect-deception-by-william-c-dietz/paperback/</x:v>
       </x:c>
-      <x:c r="S17" s="20" t="str">
-        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
+      <x:c r="S17" s="9" t="str">
+        <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -14377,7 +14371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f0c624e496a46a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58dfb15768f4082"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14442,10 +14436,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14494,7 +14488,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Enquête d’Anderson et Kahlee, vengeance de Gillian et Biotic Underground ; registre explicite des incohérences, avec propositions de gameplay mises sous contrôle éditorial.</x:v>
+        <x:v>160 fiches de production ; 7 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14513,11 +14507,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="45" t="d">
+      <x:c r="B12" s="43" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14670,22 +14664,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14934,13 +14928,13 @@
       <x:c r="F40" s="2"/>
     </x:row>
     <x:row r="41" ht="34" customHeight="1">
-      <x:c r="A41" s="30" t="str">
+      <x:c r="A41" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B41" s="31" t="str">
+      <x:c r="B41" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C41" s="32" t="str">
+      <x:c r="C41" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D41" s="2"/>
@@ -15031,10 +15025,16 @@
       <x:c r="E47" s="2"/>
       <x:c r="F47" s="2"/>
     </x:row>
-    <x:row r="48" ht="22" customHeight="1">
-      <x:c r="A48" s="2"/>
-      <x:c r="B48" s="2"/>
-      <x:c r="C48" s="2"/>
+    <x:row r="48" ht="96" customHeight="1">
+      <x:c r="A48" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>7 références supplémentaires au stade Prototype dans 1 parcours de lecture (4 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C48" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D48" s="2"/>
       <x:c r="E48" s="2"/>
       <x:c r="F48" s="2"/>
@@ -15590,6 +15590,14 @@
       <x:c r="D117" s="2"/>
       <x:c r="E117" s="2"/>
       <x:c r="F117" s="2"/>
+    </x:row>
+    <x:row r="118" ht="22" customHeight="1">
+      <x:c r="A118" s="2"/>
+      <x:c r="B118" s="2"/>
+      <x:c r="C118" s="2"/>
+      <x:c r="D118" s="2"/>
+      <x:c r="E118" s="2"/>
+      <x:c r="F118" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15731,61 +15739,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15831,10 +15839,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-NICK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nick_Donahue</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15880,10 +15888,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-TIMELINE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Timeline</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15929,10 +15937,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>DEC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200763/mass-effect-deception-by-william-c-dietz/paperback/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15978,10 +15986,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>DEC-SRC-GIL</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Gillian_Grayson</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -16027,10 +16035,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>DEC-SRC-HEN</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Hendel_Mitra</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -16076,10 +16084,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>DEC-SRC-STORY</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_III</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -16115,7 +16123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72d231c3cd774809"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f27ae4a04b4390"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16142,7 +16150,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="91" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16255,61 +16263,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16321,7 +16329,7 @@
         <x:v>Cerberus</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16340,7 +16348,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.dec.cerberus ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire DEC-REF-CERBERUS consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -16355,11 +16363,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/200763/mass-effect-deception-by-william-c-dietz/paperback/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -16370,7 +16378,7 @@
         <x:v>Biotic Underground</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16389,7 +16397,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.dec.underground ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire DEC-REF-UNDERGROUND consultable dans les lectures dec-reperes de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Matériel narratif de Deception sous réserve de cohérence avec les autres œuvres. Aucune édition corrigée n’est affirmée ; ne pas corriger silencieusement l’âge des personnages ni inventer une guérison de l’autisme.</x:v>
@@ -16404,11 +16412,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-NICK</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Nick_Donahue</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Les contradictions et réserves éditoriales de Deception restent attribuées à leurs notices. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16443,7 +16451,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c76bb03ffb94df6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a0c10961aa444ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16583,61 +16591,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16683,10 +16691,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-AND</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16732,10 +16740,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>DEC-SRC-STORY</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_III</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16771,7 +16779,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf40e068e0456401a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2632021089894ecd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16911,61 +16919,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17015,8 +17023,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17066,8 +17074,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17117,8 +17125,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17168,8 +17176,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17219,8 +17227,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17270,8 +17278,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17321,8 +17329,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17372,8 +17380,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17409,7 +17417,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc180ec0d0b534755"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R623eae4dfda64b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17549,61 +17557,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17655,8 +17663,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17708,8 +17716,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17761,8 +17769,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17814,8 +17822,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17867,8 +17875,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17920,8 +17928,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17973,8 +17981,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18026,8 +18034,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18063,7 +18071,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R194d095240a044b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc538ef82607c4148"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18203,61 +18211,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18309,8 +18317,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18360,8 +18368,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18411,8 +18419,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18462,8 +18470,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18513,8 +18521,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18564,8 +18572,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18615,8 +18623,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18666,8 +18674,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18701,7 +18709,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70eb8422cd524620"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f90e2e62ab44170"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18841,61 +18849,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18941,10 +18949,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>DEC-SRC-AND</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/David_Anderson</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18980,7 +18988,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdd87017f7c04562"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12783c22a074d3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Deception_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Deception_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcbfd759c7168486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R767331d4c4814e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R0322f1b5251646b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R0c133594f4e24867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R3c1c7568e1ef4624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R2b6f1b60505742e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R6757b90cdf0c4857"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R22c27139b38b4404"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R7c4f6ec7a5514806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1876778f1374438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R51bc823b2e624d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R07213d2937094275"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R42e25a376cfb44cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R0ca351dfd8d940ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R3908b85289e9454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R099d5efa5f664aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R377aa137b33d4359"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rdb0f56863d384889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R582aac9dfc9b4a74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcff23ae6e72141d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rf2a0e14617b44c50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rf72dc2f6a6414494"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R5407c882b30c4348"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rff52a506fe5044de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb691a1a88bae448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re28b0faf184743e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R2f39a98e721448d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb99bd41aa8914349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R889091341cb542bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1dd488caffeb45e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd2f16cf97eb24ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb3d2824051314eb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R101f19e2f7494a1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rd11a582861b54a1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbee73cc221414fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R8fb8dc1f8db94a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra6d91a95cd9b4c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Re5633d0c197942ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R058e60478a384d7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Ra1c4612bd9024457"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4e43c882201244bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2dae64a6efcd44f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb6b0e0c81ed64ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R006e5b7ca5794bb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R2f38ff74a2ff4a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R31a58df9d9004a7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rabbb447e86a34aa9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R73fbf843e29c4844"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R3f8ac09b21c74e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R581bde6a31bf4122"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb9453fe231f54ca9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5214efebba6348c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R854e37e950484d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R3d87244dc2db4752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R6bcea62080c548a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R9e43777df6354835"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4171,7 +4171,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f6561af3174015"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb18113e44aee4abc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4809,7 +4809,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7a35d767ce340d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d1eb10a3c664d42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5447,7 +5447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33a50d6c48f3461e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R832a2b95afcc4610"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6085,7 +6085,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bd34340d7194603"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaccde023d9d46d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6845,7 +6845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05ba30fb30204827"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17628131ef1b428d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7483,7 +7483,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e193e0a2ab54025"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc23516a9801c4333"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8081,7 +8081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69392d9a37194bcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb47af9c2141045a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8409,7 +8409,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc43314f3dbb94f66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbff4a4a04faa4106"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8933,7 +8933,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55e8734a7387464b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac95081bb5a949b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9359,7 +9359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04387a4fb548435d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11a4511f72f40e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9793,7 +9793,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9717aa9cd44f0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ef2fdc8e964c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10533,7 +10533,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42e15ec931974030"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R960dff8acf1348e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11273,7 +11273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0d7ca4ac98b4e34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racffd4b9e29c40f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11707,7 +11707,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae03af3f4c484739"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0799aa46fc6c4e86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12182,7 +12182,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57cbe1bf08764b09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cde53e32534bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12804,7 +12804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8660fb88b7c34c63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d2ea6ba1c554671"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13614,7 +13614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra75b034bf72b46b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9922f2244734ac8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14371,7 +14371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re58dfb15768f4082"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4c2c4bb71544a78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16123,7 +16123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f27ae4a04b4390"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bde7a0540b24900"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16451,7 +16451,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a0c10961aa444ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c660c96c5804cce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16779,7 +16779,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2632021089894ecd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra82b7eb14676416a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17417,7 +17417,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R623eae4dfda64b86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17d57ff91e1c413c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18071,7 +18071,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc538ef82607c4148"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refa22b65c7a54d5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18709,7 +18709,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f90e2e62ab44170"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re948d34b6c544731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18988,7 +18988,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb12783c22a074d3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01f0f0b235db4c8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Deception_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Deception_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R889091341cb542bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1dd488caffeb45e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd2f16cf97eb24ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb3d2824051314eb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R101f19e2f7494a1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rd11a582861b54a1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbee73cc221414fe7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R8fb8dc1f8db94a13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra6d91a95cd9b4c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Re5633d0c197942ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R058e60478a384d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Ra1c4612bd9024457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4e43c882201244bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2dae64a6efcd44f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb6b0e0c81ed64ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R006e5b7ca5794bb0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R2f38ff74a2ff4a43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R31a58df9d9004a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rabbb447e86a34aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R73fbf843e29c4844"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R3f8ac09b21c74e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R581bde6a31bf4122"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rb9453fe231f54ca9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5214efebba6348c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R854e37e950484d85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R3d87244dc2db4752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R6bcea62080c548a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R9e43777df6354835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R069ab7c19a104502"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R29dc6bae8fa04575"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R3e829feaa4ed45b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rfee307e0273b47bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R21b32a3a0fe54e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R4848c0e75a074181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rff93edb80895402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R97b03c1ce76f4982"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1a130cb47cc4475c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rbe16d20fc0d84c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rcbb93f72632f43e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1fc289f5c232483c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R22840b5de61441ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R39324d2d423f4eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rb9fdf50e844140cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R177f96170c0a4923"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Re11d40ca07414bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rfb759710abde47dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R8f18953164c7410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Reb53357f8c83441c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R392e8db8a06443f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rfa1e5120c09f41b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc341c504d50b4f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rd2acdf257ef94fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rea13fe589b714e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfa2e7795d72a41ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Ra0233c92271e4479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R9dd642161cef49c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4171,7 +4171,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb18113e44aee4abc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53da5e7867dc4050"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4809,7 +4809,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d1eb10a3c664d42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50e428101bcb4cac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5447,7 +5447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R832a2b95afcc4610"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R003bc4554e5b4b89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6085,7 +6085,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaccde023d9d46d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f3fc2cf58df456c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6845,7 +6845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17628131ef1b428d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45fbf3709da845d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7483,7 +7483,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc23516a9801c4333"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb423202270d647f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8081,7 +8081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb47af9c2141045a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6894f2c0cad24ec8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8409,7 +8409,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbff4a4a04faa4106"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44700fafa7174b58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8933,7 +8933,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac95081bb5a949b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R443fb34c61b748c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9359,7 +9359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re11a4511f72f40e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0f6c1a9834449de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9793,7 +9793,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ef2fdc8e964c13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8208727797c646a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10533,7 +10533,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R960dff8acf1348e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R957cfb54e5644c9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11273,7 +11273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racffd4b9e29c40f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a2c78c4883746d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11707,7 +11707,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0799aa46fc6c4e86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53ab0d1b96b64aed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12182,7 +12182,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cde53e32534bbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b257ea018234059"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12804,7 +12804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d2ea6ba1c554671"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19f5ae51d86b470f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13614,7 +13614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9922f2244734ac8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2bdc8acd1da435f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14371,7 +14371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4c2c4bb71544a78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5efed2a14e44ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16123,7 +16123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bde7a0540b24900"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c74154cd8e94fc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16451,7 +16451,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c660c96c5804cce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R860acbb622b14de2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16779,7 +16779,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra82b7eb14676416a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9edf26b77cf04c47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17417,7 +17417,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17d57ff91e1c413c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13e04791c569405b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18071,7 +18071,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refa22b65c7a54d5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3b7ee1c780e4f3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18709,7 +18709,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re948d34b6c544731"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bfab03681664c51"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18988,7 +18988,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01f0f0b235db4c8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f9d1576ec844345"/>
   </x:tableParts>
 </x:worksheet>
 </file>